--- a/rendusrncp/CAHIER_RECETTES_BLOC2.xlsx
+++ b/rendusrncp/CAHIER_RECETTES_BLOC2.xlsx
@@ -993,9 +993,9 @@
           <t>Réponse 200. Token Sanctum + user retournés. Redirection vers /account.</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
-        <is>
-          <t>À jouer</t>
+      <c r="I8" s="35" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="J8" s="26" t="inlineStr">
@@ -1003,7 +1003,11 @@
           <t>PHPUnit AuthTest::test_user_can_login + Cypress auth.cy.js</t>
         </is>
       </c>
-      <c r="K8" s="26" t="n"/>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 08/07/2026 : 162 tests PHPUnit backend + 39 tests Jest frontend, tous verts (AuthTest::test_user_can_login confirmé).</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -4022,9 +4026,9 @@
           <t>Réponse 200 avec products, orders, stock (revenue, by_status, low_stock).</t>
         </is>
       </c>
-      <c r="I61" s="24" t="inlineStr">
-        <is>
-          <t>À jouer</t>
+      <c r="I61" s="35" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="J61" s="26" t="inlineStr">
@@ -4032,7 +4036,11 @@
           <t>PHPUnit AdminOrderControllerTest::test_admin_can_view_stats + Cypress admin.cy.js</t>
         </is>
       </c>
-      <c r="K61" s="26" t="n"/>
+      <c r="K61" s="26" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 08/07/2026 : AdminOrderControllerTest::test_admin_can_view_stats vert (162 tests PHPUnit backend au total, tous verts).</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="75" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -4246,9 +4254,9 @@
           <t>Réponse 200 paginée (20/page). Tri descendant par id.</t>
         </is>
       </c>
-      <c r="I65" s="24" t="inlineStr">
-        <is>
-          <t>À jouer</t>
+      <c r="I65" s="35" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="J65" s="26" t="inlineStr">
@@ -4256,7 +4264,11 @@
           <t>PHPUnit AdminOrderControllerTest::test_admin_can_list_orders + Cypress admin.cy.js</t>
         </is>
       </c>
-      <c r="K65" s="26" t="n"/>
+      <c r="K65" s="26" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 08/07/2026 : AdminOrderControllerTest::test_admin_can_list_orders vert (162 tests PHPUnit backend au total, tous verts).</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="75" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -4470,9 +4482,9 @@
           <t>Réponse 201. StockLot créé. StockMovement type=in tracé.</t>
         </is>
       </c>
-      <c r="I69" s="24" t="inlineStr">
-        <is>
-          <t>À jouer</t>
+      <c r="I69" s="35" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="J69" s="26" t="inlineStr">
@@ -4480,7 +4492,11 @@
           <t>PHPUnit AdminStockControllerTest::test_admin_can_add_stock + Cypress admin-stock.cy.js</t>
         </is>
       </c>
-      <c r="K69" s="26" t="n"/>
+      <c r="K69" s="26" t="inlineStr">
+        <is>
+          <t>Suite complète rejouée le 08/07/2026 : AdminStockControllerTest::test_admin_can_add_stock vert (162 tests PHPUnit backend au total, tous verts).</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="75" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -5037,9 +5053,9 @@
           <t>Header Strict-Transport-Security retourné avec max-age et includeSubDomains.</t>
         </is>
       </c>
-      <c r="I79" s="36" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="I79" s="35" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="J79" s="26" t="inlineStr">
@@ -5049,7 +5065,7 @@
       </c>
       <c r="K79" s="26" t="inlineStr">
         <is>
-          <t>curl -I le 06/07/2026 sur prod et staging : header Strict-Transport-Security absent. Correctif déjà écrit dans infra/nginx/{prod,staging}.conf (non commité, non déployé). Voir FICHES_INCIDENTS.md / plan de correction C2.3.2.</t>
+          <t>Correctif (infra/nginx/prod.conf + staging.conf, commits 6db4d70/15a5853) déployé et vérifié en direct le 08/07/2026 : curl -I sur https://gauthierfitness.fr et https://staging.gauthierfitness.fr renvoient Strict-Transport-Security: max-age=31536000; includeSubDomains. Le commentaire précédent ("non commité, non déployé") était obsolète.</t>
         </is>
       </c>
     </row>
@@ -5094,9 +5110,9 @@
           <t>CSP présent autorisant uniquement self + js.stripe.com.</t>
         </is>
       </c>
-      <c r="I80" s="36" t="inlineStr">
-        <is>
-          <t>Échec</t>
+      <c r="I80" s="35" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -5106,7 +5122,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>curl -I le 06/07/2026 sur prod et staging : header Content-Security-Policy absent. Même cause que SEC-01, correctif prêt non déployé.</t>
+          <t>Correctif déployé et vérifié en direct le 08/07/2026 : curl -I sur prod et staging renvoient un header Content-Security-Policy restrictif (self + js.stripe.com + Sentry). Même correctif que SEC-01, même commit.</t>
         </is>
       </c>
     </row>
@@ -5782,9 +5798,9 @@
           <t>Redirection vers /login.</t>
         </is>
       </c>
-      <c r="I92" s="24" t="inlineStr">
-        <is>
-          <t>À jouer</t>
+      <c r="I92" s="35" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr">
@@ -5792,7 +5808,11 @@
           <t>Jest ProtectedRoutes.test.jsx + Cypress admin.cy.js</t>
         </is>
       </c>
-      <c r="K92" s="3" t="n"/>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>Suite Jest rejouée le 08/07/2026 : ProtectedRoute.test.jsx 3/3 vert (39 tests Jest frontend au total, tous verts).</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="75" customHeight="1">
       <c r="A93" s="25" t="inlineStr">
@@ -6064,9 +6084,9 @@
           <t>Workflow CI : PHPUnit + Pint + Build image + Trigger infra → tous verts.</t>
         </is>
       </c>
-      <c r="I97" s="24" t="inlineStr">
-        <is>
-          <t>À jouer</t>
+      <c r="I97" s="35" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="J97" s="26" t="inlineStr">
@@ -6074,7 +6094,11 @@
           <t>GitHub Actions backend ci-cd.yml</t>
         </is>
       </c>
-      <c r="K97" s="26" t="n"/>
+      <c r="K97" s="26" t="inlineStr">
+        <is>
+          <t>CI backend vérifiée verte le 08/07/2026 : sur push develop/main (ex. run GitHub Actions #28949610914) et sur pull request (ex. run #28868839895, PR GF31-V1GF-Ready -&gt; develop). ci-cd.yml se déclenche bien sur push ET pull_request vers main/develop.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -6117,9 +6141,9 @@
           <t>Workflow CI : ESLint + Build Vite + Jest + Build image → tous verts.</t>
         </is>
       </c>
-      <c r="I98" s="24" t="inlineStr">
-        <is>
-          <t>À jouer</t>
+      <c r="I98" s="35" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="J98" s="3" t="inlineStr">
@@ -6127,7 +6151,11 @@
           <t>GitHub Actions frontend ci-cd.yml</t>
         </is>
       </c>
-      <c r="K98" s="3" t="n"/>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>CI frontend vérifiée verte le 08/07/2026 : sur push develop/main (ex. run #28925409791) et sur pull request (ex. run Dependabot #28925617135). ci-cd.yml se déclenche bien sur push ET pull_request vers main/develop.</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="25" t="inlineStr">
@@ -6171,9 +6199,9 @@
           <t>Staging green. E2E Cypress green. Prod deploy manuel OK avec health check 200 à la fin.</t>
         </is>
       </c>
-      <c r="I99" s="24" t="inlineStr">
-        <is>
-          <t>À jouer</t>
+      <c r="I99" s="35" t="inlineStr">
+        <is>
+          <t>Passé</t>
         </is>
       </c>
       <c r="J99" s="26" t="inlineStr">
@@ -6181,7 +6209,11 @@
           <t>GitHub Actions infra deploy.yml</t>
         </is>
       </c>
-      <c r="K99" s="26" t="n"/>
+      <c r="K99" s="26" t="inlineStr">
+        <is>
+          <t>Pipeline complet vérifié le 08/07/2026 : run infra #28949784465 (staging, déclenché par repository_dispatch après CI backend/frontend) -&gt; Staging Deployment vert (48s) -&gt; Tests E2E Cypress vert (1m24s). Déploiement prod le plus récent : run #28883415233 (workflow_dispatch manuel, 07/07/2026, vert, 42s). Health check confirmé en direct le 08/07/2026 : GET https://gauthierfitness.fr/api/health -&gt; 200 {"status":"ok"}.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A5:K98"/>
@@ -6217,6 +6249,7 @@
       <c r="C1" s="28" t="n"/>
       <c r="D1" s="29" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="32" t="inlineStr">
         <is>
@@ -6367,6 +6400,8 @@
         <v>2</v>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
         <is>
@@ -6427,6 +6462,8 @@
         <v>3</v>
       </c>
     </row>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="32" t="inlineStr">
         <is>
@@ -6477,6 +6514,8 @@
         <v>4</v>
       </c>
     </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="32" t="inlineStr">
         <is>
@@ -6504,7 +6543,7 @@
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38">
@@ -6514,7 +6553,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -6524,9 +6563,10 @@
         </is>
       </c>
       <c r="B39" s="14" t="n">
-        <v>8</v>
-      </c>
-    </row>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
         <is>
